--- a/saidas/historico_runs/historico_runs_2026_08_28.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_08_28.xlsx
@@ -5791,34 +5791,34 @@
         <v>45</v>
       </c>
       <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>43</v>
+      </c>
+      <c r="H87" t="n">
         <v>2</v>
       </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" t="n">
-        <v>41</v>
-      </c>
-      <c r="H87" t="n">
-        <v>4</v>
-      </c>
       <c r="I87" t="n">
-        <v>0.374</v>
+        <v>-0.031</v>
       </c>
       <c r="J87" t="n">
-        <v>0.662</v>
+        <v>-0.031</v>
       </c>
       <c r="K87" t="n">
-        <v>0.356</v>
+        <v>0.27</v>
       </c>
       <c r="L87" t="n">
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>11</v>
       </c>
       <c r="R87" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
     </row>
   </sheetData>
@@ -5851,7 +5851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O604"/>
+  <dimension ref="A1:O602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42422,31 +42422,31 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Monitorar CALL</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Monitorar CALL</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>0.4415</v>
+        <v>0.2803</v>
       </c>
       <c r="F601" t="n">
-        <v>1.054078</v>
+        <v>1.079039</v>
       </c>
       <c r="G601" t="n">
-        <v>2.4774</v>
+        <v>1.0065</v>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>monitorar_e6_quase_nivel_a</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -42455,28 +42455,28 @@
         </is>
       </c>
       <c r="J601" t="n">
-        <v>0.6017</v>
+        <v>0.5395</v>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="L601" t="n">
-        <v>0.6017</v>
+        <v>0.2698</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Sem estrutura com edge positivo — não operar</t>
         </is>
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="O601" t="n">
-        <v>0.6624</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="602">
@@ -42485,31 +42485,31 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>0.3443</v>
+        <v>0.2698</v>
       </c>
       <c r="F602" t="n">
-        <v>1.056579</v>
+        <v>1.121181</v>
       </c>
       <c r="G602" t="n">
-        <v>1.0151</v>
+        <v>1.7119</v>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>monitorar_e6_quase_nivel_a</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -42518,15 +42518,15 @@
         </is>
       </c>
       <c r="J602" t="n">
-        <v>0.5276</v>
+        <v>0.5799</v>
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="L602" t="n">
-        <v>0.2638</v>
+        <v>0.5799</v>
       </c>
       <c r="M602" t="inlineStr">
         <is>
@@ -42539,133 +42539,7 @@
         </is>
       </c>
       <c r="O602" t="n">
-        <v>0.0152</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="E603" t="n">
-        <v>0.3062</v>
-      </c>
-      <c r="F603" t="n">
-        <v>1.109768</v>
-      </c>
-      <c r="G603" t="n">
-        <v>1.8834</v>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>monitorar_e6_quase_nivel_a</t>
-        </is>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J603" t="n">
-        <v>0.5897</v>
-      </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="L603" t="n">
-        <v>0.2948</v>
-      </c>
-      <c r="M603" t="inlineStr">
-        <is>
-          <t>Sem estrutura com edge positivo — não operar</t>
-        </is>
-      </c>
-      <c r="N603" t="inlineStr">
-        <is>
-          <t>baixa</t>
-        </is>
-      </c>
-      <c r="O603" t="n">
-        <v>-0.0292</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>SBFG3</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E604" t="n">
-        <v>0.2705</v>
-      </c>
-      <c r="F604" t="n">
-        <v>1.334733</v>
-      </c>
-      <c r="G604" t="n">
-        <v>0.8265</v>
-      </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J604" t="n">
-        <v>0.4639</v>
-      </c>
-      <c r="K604" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="L604" t="n">
-        <v>0.4639</v>
-      </c>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="N604" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="O604" t="n">
-        <v>0.0864</v>
+        <v>-0.0311</v>
       </c>
     </row>
   </sheetData>
@@ -43019,52 +42893,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46262</v>
+        <v>46180</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.08599999999999999</v>
-      </c>
+          <t>Alerta PUT, Compra CALL, Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46180</v>
+        <v>46261</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alerta PUT, Compra CALL, Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>Alerta CALL, Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.08599999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43119,55 +42993,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46173</v>
+        <v>46160</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46262</v>
+        <v>46227</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
+          <t>Alerta CALL, Monitorar CALL</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.651</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.662</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46160</v>
+        <v>46173</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46227</v>
+        <v>46261</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alerta CALL, Monitorar CALL</t>
+          <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="19">

--- a/saidas/historico_runs/historico_runs_2026_08_28.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_08_28.xlsx
@@ -5791,7 +5791,7 @@
         <v>45</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -5800,22 +5800,22 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L87" t="n">
         <v>2</v>
-      </c>
-      <c r="I87" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="J87" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R87" t="n">
-        <v>0.205</v>
+        <v>0.222</v>
       </c>
     </row>
   </sheetData>
@@ -5851,7 +5851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O602"/>
+  <dimension ref="A1:O603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42436,13 +42436,13 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>0.2803</v>
+        <v>0.2746</v>
       </c>
       <c r="F601" t="n">
-        <v>1.079039</v>
+        <v>1.083631</v>
       </c>
       <c r="G601" t="n">
-        <v>1.0065</v>
+        <v>1.0582</v>
       </c>
       <c r="H601" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         </is>
       </c>
       <c r="J601" t="n">
-        <v>0.5395</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="K601" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         </is>
       </c>
       <c r="L601" t="n">
-        <v>0.2698</v>
+        <v>0.273</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
@@ -42485,61 +42485,124 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
+          <t>CPLE3</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Alerta CALL</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>0.1987</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1.19085</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>alerta_executor_nivel_B</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J602" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="L602" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Bull spread largo: compra call delta~45, venda call delta~15</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="O602" t="n">
+        <v>0.1613</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
           <t>KLBN11</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
+      <c r="C603" t="inlineStr">
         <is>
           <t>Compra CALL</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr">
+      <c r="D603" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E602" t="n">
-        <v>0.2698</v>
-      </c>
-      <c r="F602" t="n">
-        <v>1.121181</v>
-      </c>
-      <c r="G602" t="n">
-        <v>1.7119</v>
-      </c>
-      <c r="H602" t="inlineStr">
+      <c r="E603" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1.122789</v>
+      </c>
+      <c r="G603" t="n">
+        <v>1.6929</v>
+      </c>
+      <c r="H603" t="inlineStr">
         <is>
           <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J602" t="n">
-        <v>0.5799</v>
-      </c>
-      <c r="K602" t="inlineStr">
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>forte</t>
+        </is>
+      </c>
+      <c r="J603" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="K603" t="inlineStr">
         <is>
           <t>HAR</t>
         </is>
       </c>
-      <c r="L602" t="n">
-        <v>0.5799</v>
-      </c>
-      <c r="M602" t="inlineStr">
+      <c r="L603" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="M603" t="inlineStr">
         <is>
           <t>Sem estrutura com edge positivo — não operar</t>
         </is>
       </c>
-      <c r="N602" t="inlineStr">
+      <c r="N603" t="inlineStr">
         <is>
           <t>baixa</t>
         </is>
       </c>
-      <c r="O602" t="n">
-        <v>-0.0311</v>
+      <c r="O603" t="n">
+        <v>-0.0313</v>
       </c>
     </row>
   </sheetData>
@@ -43701,28 +43764,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SMAL11</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Monitorar CALL</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="46">
@@ -43809,7 +43872,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -43823,14 +43886,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.015</v>
+        <v>0.161</v>
       </c>
       <c r="G49" t="n">
-        <v>0.015</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="50">
@@ -43913,17 +43976,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>SMAL11</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46210</v>
+        <v>46253</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46211</v>
+        <v>46254</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -43931,37 +43994,37 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.385</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.385</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-0.162</v>
+        <v>0.385</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.162</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="55">
@@ -43990,17 +44053,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46261</v>
+        <v>46202</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46261</v>
+        <v>46202</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -44008,10 +44071,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.161</v>
+        <v>-0.162</v>
       </c>
       <c r="G56" t="n">
-        <v>0.161</v>
+        <v>-0.162</v>
       </c>
     </row>
     <row r="57">
